--- a/sienna-art-studio-admin/samples/sienna-test-import.xlsx
+++ b/sienna-art-studio-admin/samples/sienna-test-import.xlsx
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="377">
   <si>
     <t>How to use this file</t>
   </si>
@@ -1306,9 +1306,6 @@
   </si>
   <si>
     <t>test-delete-me</t>
-  </si>
-  <si>
-    <t>draft</t>
   </si>
 </sst>
 </file>
@@ -6599,7 +6596,7 @@
         <v>376</v>
       </c>
       <c r="H301" t="s">
-        <v>377</v>
+        <v>157</v>
       </c>
       <c r="I301" t="s">
         <v>164</v>
